--- a/output/roomself_excel/2086.xlsx
+++ b/output/roomself_excel/2086.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>79380</v>
+        <v>209168</v>
       </c>
       <c r="D2" t="n">
-        <v>3632</v>
+        <v>3716</v>
       </c>
       <c r="E2" t="n">
-        <v>841</v>
+        <v>419</v>
       </c>
       <c r="F2" t="n">
-        <v>127</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>217239</v>
+        <v>450500</v>
       </c>
       <c r="D3" t="n">
-        <v>4152</v>
+        <v>6708</v>
       </c>
       <c r="E3" t="n">
-        <v>695</v>
+        <v>1118</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4">
@@ -510,17 +510,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13596</v>
+        <v>199482</v>
       </c>
       <c r="D4" t="n">
-        <v>940</v>
+        <v>3620</v>
       </c>
       <c r="E4" t="n">
-        <v>132</v>
+        <v>395</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67053</v>
+        <v>206980</v>
       </c>
       <c r="D5" t="n">
-        <v>3016</v>
+        <v>3676</v>
       </c>
       <c r="E5" t="n">
-        <v>680</v>
+        <v>395</v>
       </c>
       <c r="F5" t="n">
-        <v>132</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>286570</v>
+        <v>17654</v>
       </c>
       <c r="D6" t="n">
-        <v>4468</v>
+        <v>1116</v>
       </c>
       <c r="E6" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20152</v>
+        <v>14746</v>
       </c>
       <c r="D7" t="n">
-        <v>1268</v>
+        <v>988</v>
       </c>
       <c r="E7" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>336756</v>
+        <v>26900</v>
       </c>
       <c r="D8" t="n">
-        <v>4880</v>
+        <v>1476</v>
       </c>
       <c r="E8" t="n">
-        <v>695</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>571</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17654</v>
+        <v>31861</v>
       </c>
       <c r="D9" t="n">
-        <v>1116</v>
+        <v>1448</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -642,14 +642,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13575</v>
+        <v>16157</v>
       </c>
       <c r="D10" t="n">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6375</v>
+        <v>16060</v>
       </c>
       <c r="D11" t="n">
-        <v>640</v>
+        <v>1024</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8475</v>
+        <v>171039</v>
       </c>
       <c r="D12" t="n">
-        <v>752</v>
+        <v>5796</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1118</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -708,14 +708,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8025</v>
+        <v>43362</v>
       </c>
       <c r="D13" t="n">
-        <v>728</v>
+        <v>1772</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -730,14 +730,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6300</v>
+        <v>44384</v>
       </c>
       <c r="D14" t="n">
-        <v>636</v>
+        <v>1800</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12225</v>
+        <v>41811</v>
       </c>
       <c r="D15" t="n">
-        <v>952</v>
+        <v>1648</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>261051</v>
+        <v>20152</v>
       </c>
       <c r="D16" t="n">
-        <v>4208</v>
+        <v>1268</v>
       </c>
       <c r="E16" t="n">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>246078</v>
+        <v>13575</v>
       </c>
       <c r="D17" t="n">
-        <v>4116</v>
+        <v>1024</v>
       </c>
       <c r="E17" t="n">
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>285131</v>
+        <v>12225</v>
       </c>
       <c r="D18" t="n">
-        <v>4460</v>
+        <v>952</v>
       </c>
       <c r="E18" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>325584</v>
+        <v>53625</v>
       </c>
       <c r="D19" t="n">
-        <v>4824</v>
+        <v>1960</v>
       </c>
       <c r="E19" t="n">
-        <v>668</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>70928</v>
+        <v>68352</v>
       </c>
       <c r="D20" t="n">
-        <v>2784</v>
+        <v>2092</v>
       </c>
       <c r="E20" t="n">
-        <v>603</v>
+        <v>307</v>
       </c>
       <c r="F20" t="n">
-        <v>155</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14880</v>
+        <v>79380</v>
       </c>
       <c r="D21" t="n">
-        <v>976</v>
+        <v>3632</v>
       </c>
       <c r="E21" t="n">
-        <v>120</v>
+        <v>841</v>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17172</v>
+        <v>217239</v>
       </c>
       <c r="D22" t="n">
-        <v>1068</v>
+        <v>4152</v>
       </c>
       <c r="E22" t="n">
-        <v>159</v>
+        <v>695</v>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>67500</v>
+        <v>13596</v>
       </c>
       <c r="D23" t="n">
-        <v>2932</v>
+        <v>940</v>
       </c>
       <c r="E23" t="n">
-        <v>654</v>
+        <v>132</v>
       </c>
       <c r="F23" t="n">
-        <v>139</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>108120</v>
+        <v>67053</v>
       </c>
       <c r="D24" t="n">
-        <v>4648</v>
+        <v>3016</v>
       </c>
       <c r="E24" t="n">
-        <v>1118</v>
+        <v>680</v>
       </c>
       <c r="F24" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25">
@@ -972,20 +972,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14746</v>
+        <v>286570</v>
       </c>
       <c r="D25" t="n">
-        <v>988</v>
+        <v>4468</v>
       </c>
       <c r="E25" t="n">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="F25" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
@@ -994,17 +994,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>209168</v>
+        <v>336756</v>
       </c>
       <c r="D26" t="n">
-        <v>3716</v>
+        <v>4880</v>
       </c>
       <c r="E26" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F26" t="n">
         <v>29</v>
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>204510</v>
+        <v>6375</v>
       </c>
       <c r="D27" t="n">
-        <v>3644</v>
+        <v>640</v>
       </c>
       <c r="E27" t="n">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1038,20 +1038,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>199482</v>
+        <v>8475</v>
       </c>
       <c r="D28" t="n">
-        <v>3620</v>
+        <v>752</v>
       </c>
       <c r="E28" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>450500</v>
+        <v>8025</v>
       </c>
       <c r="D29" t="n">
-        <v>6708</v>
+        <v>728</v>
       </c>
       <c r="E29" t="n">
-        <v>1118</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>20460</v>
+        <v>6300</v>
       </c>
       <c r="D30" t="n">
-        <v>1156</v>
+        <v>636</v>
       </c>
       <c r="E30" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1104,20 +1104,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>171039</v>
+        <v>261051</v>
       </c>
       <c r="D31" t="n">
-        <v>5796</v>
+        <v>4208</v>
       </c>
       <c r="E31" t="n">
-        <v>1118</v>
+        <v>401</v>
       </c>
       <c r="F31" t="n">
-        <v>142</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
@@ -1126,20 +1126,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>43362</v>
+        <v>246078</v>
       </c>
       <c r="D32" t="n">
-        <v>1772</v>
+        <v>4116</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
@@ -1148,20 +1148,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>53625</v>
+        <v>285131</v>
       </c>
       <c r="D33" t="n">
-        <v>1960</v>
+        <v>4460</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34">
@@ -1174,16 +1174,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>74812</v>
+        <v>325584</v>
       </c>
       <c r="D34" t="n">
-        <v>3008</v>
+        <v>4824</v>
       </c>
       <c r="E34" t="n">
-        <v>669</v>
+        <v>408</v>
       </c>
       <c r="F34" t="n">
-        <v>137</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>593684</v>
+        <v>70928</v>
       </c>
       <c r="D35" t="n">
-        <v>10288</v>
+        <v>2784</v>
       </c>
       <c r="E35" t="n">
-        <v>1364</v>
+        <v>603</v>
       </c>
       <c r="F35" t="n">
-        <v>778</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>90525</v>
+        <v>14880</v>
       </c>
       <c r="D36" t="n">
-        <v>2440</v>
+        <v>976</v>
       </c>
       <c r="E36" t="n">
-        <v>343</v>
+        <v>120</v>
       </c>
       <c r="F36" t="n">
-        <v>278</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37">
@@ -1236,20 +1236,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>26900</v>
+        <v>17172</v>
       </c>
       <c r="D37" t="n">
-        <v>1476</v>
+        <v>1068</v>
       </c>
       <c r="E37" t="n">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="F37" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>92445</v>
+        <v>67500</v>
       </c>
       <c r="D38" t="n">
-        <v>2604</v>
+        <v>2932</v>
       </c>
       <c r="E38" t="n">
-        <v>464</v>
+        <v>654</v>
       </c>
       <c r="F38" t="n">
-        <v>233</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39">
@@ -1284,16 +1284,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11680</v>
+        <v>108120</v>
       </c>
       <c r="D39" t="n">
-        <v>904</v>
+        <v>4648</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1118</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40">
@@ -1306,16 +1306,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>27720</v>
+        <v>204510</v>
       </c>
       <c r="D40" t="n">
-        <v>1332</v>
+        <v>3644</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41">
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11388</v>
+        <v>20460</v>
       </c>
       <c r="D41" t="n">
-        <v>896</v>
+        <v>1156</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42">
@@ -1350,16 +1350,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>214864</v>
+        <v>74812</v>
       </c>
       <c r="D42" t="n">
-        <v>3772</v>
+        <v>3008</v>
       </c>
       <c r="E42" t="n">
-        <v>419</v>
+        <v>669</v>
       </c>
       <c r="F42" t="n">
-        <v>29</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43">
@@ -1372,16 +1372,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>210124</v>
+        <v>593684</v>
       </c>
       <c r="D43" t="n">
-        <v>3700</v>
+        <v>10288</v>
       </c>
       <c r="E43" t="n">
-        <v>401</v>
+        <v>1364</v>
       </c>
       <c r="F43" t="n">
-        <v>29</v>
+        <v>778</v>
       </c>
     </row>
     <row r="44">
@@ -1390,20 +1390,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>206980</v>
+        <v>90525</v>
       </c>
       <c r="D44" t="n">
-        <v>3676</v>
+        <v>2440</v>
       </c>
       <c r="E44" t="n">
-        <v>395</v>
+        <v>343</v>
       </c>
       <c r="F44" t="n">
-        <v>29</v>
+        <v>278</v>
       </c>
     </row>
     <row r="45">
@@ -1412,20 +1412,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>31861</v>
+        <v>92445</v>
       </c>
       <c r="D45" t="n">
-        <v>1448</v>
+        <v>2604</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46">
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>50907</v>
+        <v>11680</v>
       </c>
       <c r="D46" t="n">
-        <v>1808</v>
+        <v>904</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -1456,14 +1456,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>44384</v>
+        <v>27720</v>
       </c>
       <c r="D47" t="n">
-        <v>1800</v>
+        <v>1332</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>12861</v>
+        <v>11388</v>
       </c>
       <c r="D48" t="n">
-        <v>1048</v>
+        <v>896</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -1504,16 +1504,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>72162</v>
+        <v>214864</v>
       </c>
       <c r="D49" t="n">
-        <v>2212</v>
+        <v>3772</v>
       </c>
       <c r="E49" t="n">
-        <v>221</v>
+        <v>419</v>
       </c>
       <c r="F49" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
@@ -1522,20 +1522,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>68352</v>
+        <v>210124</v>
       </c>
       <c r="D50" t="n">
-        <v>2092</v>
+        <v>3700</v>
       </c>
       <c r="E50" t="n">
-        <v>307</v>
+        <v>401</v>
       </c>
       <c r="F50" t="n">
-        <v>278</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51">
@@ -1548,16 +1548,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>41600</v>
+        <v>50907</v>
       </c>
       <c r="D51" t="n">
-        <v>1632</v>
+        <v>1808</v>
       </c>
       <c r="E51" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1566,14 +1566,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>16157</v>
+        <v>12861</v>
       </c>
       <c r="D52" t="n">
-        <v>1032</v>
+        <v>1048</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -1588,20 +1588,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>41811</v>
+        <v>72162</v>
       </c>
       <c r="D53" t="n">
-        <v>1648</v>
+        <v>2212</v>
       </c>
       <c r="E53" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F53" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>14299</v>
+        <v>41600</v>
       </c>
       <c r="D54" t="n">
-        <v>1040</v>
+        <v>1632</v>
       </c>
       <c r="E54" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F54" t="n">
-        <v>102</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55">
@@ -1632,20 +1632,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>16060</v>
+        <v>14299</v>
       </c>
       <c r="D55" t="n">
-        <v>1024</v>
+        <v>1040</v>
       </c>
       <c r="E55" t="n">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="F55" t="n">
-        <v>29</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56">

--- a/output/roomself_excel/2086.xlsx
+++ b/output/roomself_excel/2086.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,26 @@
       <c r="D2" t="n">
         <v>3716</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>419</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>29</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +561,26 @@
       <c r="D3" t="n">
         <v>6708</v>
       </c>
-      <c r="E3" t="n">
-        <v>1118</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>433</v>
-      </c>
+        <v>866</v>
+      </c>
+      <c r="G3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +597,26 @@
       <c r="D4" t="n">
         <v>3620</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>395</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>29</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +633,26 @@
       <c r="D5" t="n">
         <v>3676</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>395</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>29</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +669,18 @@
       <c r="D6" t="n">
         <v>1116</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +697,26 @@
       <c r="D7" t="n">
         <v>988</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>146</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>29</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +733,26 @@
       <c r="D8" t="n">
         <v>1476</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>100</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>23</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +769,18 @@
       <c r="D9" t="n">
         <v>1448</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +797,18 @@
       <c r="D10" t="n">
         <v>1032</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +825,26 @@
       <c r="D11" t="n">
         <v>1024</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>146</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>29</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +861,34 @@
       <c r="D12" t="n">
         <v>5796</v>
       </c>
-      <c r="E12" t="n">
-        <v>1118</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>142</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="G12" t="n">
+        <v>29</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>391</v>
+      </c>
+      <c r="J12" t="n">
+        <v>29</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +905,18 @@
       <c r="D13" t="n">
         <v>1772</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +933,18 @@
       <c r="D14" t="n">
         <v>1800</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +961,26 @@
       <c r="D15" t="n">
         <v>1648</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>231</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>23</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +997,18 @@
       <c r="D16" t="n">
         <v>1268</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1025,18 @@
       <c r="D17" t="n">
         <v>1024</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1053,18 @@
       <c r="D18" t="n">
         <v>952</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1081,18 @@
       <c r="D19" t="n">
         <v>1960</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1109,34 @@
       <c r="D20" t="n">
         <v>2092</v>
       </c>
-      <c r="E20" t="n">
-        <v>307</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>278</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="G20" t="n">
+        <v>22</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>256</v>
+      </c>
+      <c r="J20" t="n">
+        <v>23</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1153,34 @@
       <c r="D21" t="n">
         <v>3632</v>
       </c>
-      <c r="E21" t="n">
-        <v>841</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>127</v>
-      </c>
+        <v>810</v>
+      </c>
+      <c r="G21" t="n">
+        <v>29</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>98</v>
+      </c>
+      <c r="J21" t="n">
+        <v>31</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1197,26 @@
       <c r="D22" t="n">
         <v>4152</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>695</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>29</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1233,26 @@
       <c r="D23" t="n">
         <v>940</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>132</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>29</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1269,34 @@
       <c r="D24" t="n">
         <v>3016</v>
       </c>
-      <c r="E24" t="n">
-        <v>680</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>132</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="G24" t="n">
+        <v>29</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>103</v>
+      </c>
+      <c r="J24" t="n">
+        <v>29</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1313,26 @@
       <c r="D25" t="n">
         <v>4468</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>410</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>31</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1349,26 @@
       <c r="D26" t="n">
         <v>4880</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>422</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>29</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1385,18 @@
       <c r="D27" t="n">
         <v>640</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1413,18 @@
       <c r="D28" t="n">
         <v>752</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,12 +1441,18 @@
       <c r="D29" t="n">
         <v>728</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,12 +1469,18 @@
       <c r="D30" t="n">
         <v>636</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1497,26 @@
       <c r="D31" t="n">
         <v>4208</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>401</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>31</v>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1135,12 +1533,26 @@
       <c r="D32" t="n">
         <v>4116</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>378</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>31</v>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1157,12 +1569,26 @@
       <c r="D33" t="n">
         <v>4460</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>408</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>31</v>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1179,12 +1605,26 @@
       <c r="D34" t="n">
         <v>4824</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>408</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>29</v>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1201,12 +1641,34 @@
       <c r="D35" t="n">
         <v>2784</v>
       </c>
-      <c r="E35" t="n">
-        <v>603</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F35" t="n">
-        <v>155</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="G35" t="n">
+        <v>31</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>572</v>
+      </c>
+      <c r="J35" t="n">
+        <v>31</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1223,12 +1685,26 @@
       <c r="D36" t="n">
         <v>976</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>120</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>31</v>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1245,12 +1721,26 @@
       <c r="D37" t="n">
         <v>1068</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>159</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>31</v>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1267,12 +1757,34 @@
       <c r="D38" t="n">
         <v>2932</v>
       </c>
-      <c r="E38" t="n">
-        <v>654</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F38" t="n">
-        <v>139</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="G38" t="n">
+        <v>29</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>625</v>
+      </c>
+      <c r="J38" t="n">
+        <v>31</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1289,12 +1801,34 @@
       <c r="D39" t="n">
         <v>4648</v>
       </c>
-      <c r="E39" t="n">
-        <v>1118</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F39" t="n">
-        <v>131</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G39" t="n">
+        <v>29</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1014</v>
+      </c>
+      <c r="J39" t="n">
+        <v>29</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1311,12 +1845,26 @@
       <c r="D40" t="n">
         <v>3644</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>401</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>29</v>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1333,12 +1881,26 @@
       <c r="D41" t="n">
         <v>1156</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>165</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>29</v>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1355,11 +1917,49 @@
       <c r="D42" t="n">
         <v>3008</v>
       </c>
-      <c r="E42" t="n">
-        <v>669</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F42" t="n">
-        <v>137</v>
+        <v>118</v>
+      </c>
+      <c r="G42" t="n">
+        <v>19</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>616</v>
+      </c>
+      <c r="J42" t="n">
+        <v>19</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>18</v>
+      </c>
+      <c r="M42" t="n">
+        <v>18</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>118</v>
+      </c>
+      <c r="P42" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -1377,12 +1977,42 @@
       <c r="D43" t="n">
         <v>10288</v>
       </c>
-      <c r="E43" t="n">
-        <v>1364</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F43" t="n">
-        <v>778</v>
-      </c>
+        <v>1996</v>
+      </c>
+      <c r="G43" t="n">
+        <v>46</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>686</v>
+      </c>
+      <c r="J43" t="n">
+        <v>46</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>686</v>
+      </c>
+      <c r="M43" t="n">
+        <v>45</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1399,12 +2029,34 @@
       <c r="D44" t="n">
         <v>2440</v>
       </c>
-      <c r="E44" t="n">
-        <v>343</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F44" t="n">
-        <v>278</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="G44" t="n">
+        <v>23</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>319</v>
+      </c>
+      <c r="J44" t="n">
+        <v>22</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1421,12 +2073,34 @@
       <c r="D45" t="n">
         <v>2604</v>
       </c>
-      <c r="E45" t="n">
-        <v>464</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F45" t="n">
-        <v>233</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="G45" t="n">
+        <v>23</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>441</v>
+      </c>
+      <c r="J45" t="n">
+        <v>23</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1443,12 +2117,18 @@
       <c r="D46" t="n">
         <v>904</v>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1465,12 +2145,18 @@
       <c r="D47" t="n">
         <v>1332</v>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1487,12 +2173,18 @@
       <c r="D48" t="n">
         <v>896</v>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1509,12 +2201,26 @@
       <c r="D49" t="n">
         <v>3772</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
         <v>419</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>29</v>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1531,12 +2237,26 @@
       <c r="D50" t="n">
         <v>3700</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
         <v>401</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>29</v>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1553,12 +2273,18 @@
       <c r="D51" t="n">
         <v>1808</v>
       </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1575,12 +2301,18 @@
       <c r="D52" t="n">
         <v>1048</v>
       </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1597,12 +2329,26 @@
       <c r="D53" t="n">
         <v>2212</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
         <v>221</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>46</v>
       </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1619,12 +2365,26 @@
       <c r="D54" t="n">
         <v>1632</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
         <v>200</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>46</v>
       </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1641,12 +2401,34 @@
       <c r="D55" t="n">
         <v>1040</v>
       </c>
-      <c r="E55" t="n">
-        <v>204</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F55" t="n">
-        <v>102</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="G55" t="n">
+        <v>23</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>79</v>
+      </c>
+      <c r="J55" t="n">
+        <v>23</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1663,12 +2445,26 @@
       <c r="D56" t="n">
         <v>956</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
         <v>151</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>46</v>
       </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1685,12 +2481,26 @@
       <c r="D57" t="n">
         <v>984</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
         <v>164</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>29</v>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1707,12 +2517,18 @@
       <c r="D58" t="n">
         <v>724</v>
       </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1729,12 +2545,18 @@
       <c r="D59" t="n">
         <v>662</v>
       </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
